--- a/Quizbot/data/QUESTIONS.xlsx
+++ b/Quizbot/data/QUESTIONS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\++My Codes\Web Develop\Telegam_Bale Bot\Keramat_Quizbot2\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\++My Codes\Web Develop\Telegam_Bale Bot\Keramat_Quizbot2\Quizbot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41290341-325F-44DE-9A96-B8C6E2C52056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8091F966-1A08-477A-BF37-3A68A6E117B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
   <si>
     <t>q_index</t>
   </si>
@@ -60,91 +60,94 @@
     <t>ه</t>
   </si>
   <si>
-    <t>مهمون اومده و بچتون نمی‌خواد توی مهمونی شرکت کنه و میخواد تو  اتاقش بمونه. از شما هم می‌خواد از مهمون‌ها پنهان کنین که تو اتاقه</t>
-  </si>
-  <si>
-    <t>وقت انتخاب رشته دبیرستان فرزندتون رسیده. و شما فکر میکنید انتخابش آینده شغلی و تحصیلی خوبی نداره و عاقلانه نیست</t>
-  </si>
-  <si>
-    <t>برای تفریح رفتین پارک، اجازه میدین از چه وسیله‌ای استفاده کنه</t>
-  </si>
-  <si>
-    <t>فرض کنید فرزند 12 ساله‌ای دارید که می‌خواد آشپزی کنه:</t>
-  </si>
-  <si>
-    <t>دلیل بی‌میلیشو برای نبودن در میهمانی رو می‌پرسم</t>
-  </si>
-  <si>
-    <t>تلاش می‌کنم تجربه کوتاهی در رشته‌های دیگر پیدا کنه</t>
-  </si>
-  <si>
-    <t>فقط یک وسیله اونم در زمان محدود</t>
-  </si>
-  <si>
-    <t>استخر توپ</t>
-  </si>
-  <si>
-    <t>تاب سواری</t>
-  </si>
-  <si>
-    <t>بازی در جای سربسته</t>
-  </si>
-  <si>
-    <t>وسایل مورد نیازش رو براش فراهم می‌کنم</t>
-  </si>
-  <si>
-    <t>ازش می‌خوام تو آماده کردن بخشی از غذا به من کمک کنه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عاشق بستنیه، برای اینکه از دلش دربیارم سریع میپرم براش بستنی می‌خرم </t>
-  </si>
-  <si>
-    <t>عذرخواهی می‌کنم ولی ازش می‌خواهم از اینجا به بعد بیشتر حواسش به نظم خونه باشه</t>
-  </si>
-  <si>
-    <t>چه معنی میده والا، هر چی دم دستم باشه شوت می‌کنم سمتش</t>
-  </si>
-  <si>
-    <t>برای لحن تند و عصبانیم عذرخواهی می‌کنم و اعتراف می‌کنم که تشخیص من اشتباه بوده</t>
-  </si>
-  <si>
-    <t>میفهمم اشتباه کردم برای همین به روی خودم نمیارم و بحث و ناراحتی رو ادامه نمی‌دم</t>
-  </si>
-  <si>
-    <t>به زور در اتاقشو باز می‌ذارم و بلند به همه مهمونا می‌گم که خونه اس تا بلکم خجالت بکشه</t>
-  </si>
-  <si>
     <t>چه معنی داره؟ اصلا نمی‌پذیرم چون هم تعاملش با مهمونا مهمه و هم باید کمکم کنه</t>
   </si>
   <si>
-    <t>خط قرمز پنهان‌کاری و دروغگویی رو دوباره بهش گوشزد میکنم</t>
-  </si>
-  <si>
-    <t>از اینکه دلش نمی‌خواد تو مهمونی شرکت کنه ناراحت می‌شم و بهش هم میگم ولی به حرفش عمل می‌کنم</t>
-  </si>
-  <si>
-    <t>دختر عمه پروین رو بهش یاداوری میکنم که چه تجربه ناموفقی داشته</t>
-  </si>
-  <si>
-    <t>چون  حال خوبش برام مهمتر از همه چیزه اجازه می‌دهم خودش انتخاب کنه</t>
-  </si>
-  <si>
-    <t>اگر خیلی اصرار به رشته خاصی کند اجازه ادامه تحصیل به او نمی‌دهم</t>
-  </si>
-  <si>
-    <t>یکبار مسیر کلی که با هم طراحی کردیم رو بررسی می‌کنیم تا متوجه شویم این رشته برای این مسیر کارآمد هست یا نه</t>
-  </si>
-  <si>
-    <t>هر وسیله‌ای که دلش بخواد بدون محدودیت زمانی میتونه استفاده کنه</t>
-  </si>
-  <si>
-    <t>یه لیست از غذاهایی که فکر میکنم آماده کردنش برایش راحتتره بهش می‌دم</t>
-  </si>
-  <si>
-    <t>تمام مدت کنارش می‌مونم که اگر کمکی خواست باشم و سعی میکنم فیلم هم بگیرم که خاطره بشه</t>
-  </si>
-  <si>
-    <t>وا آشپزخونه جای کسی جز خودم نیست حتما اونجا رو به هم میریزه من باید 5 ساعت وایستم تمیز کنم</t>
+    <t>غذا از دیشب بیرون یخچال مونده و فاسد شده. با عصبانیت میدوین سمت بچه و دعواش می‌کنین. ولی می‌فهمین تشخیص شما غلط بوده و اون بچه تقصیری نداشته 😶‍🌫️</t>
+  </si>
+  <si>
+    <t>برای لحن تند و عصبانیم عذرخواهی می‌کنم و بهش میگم من اشتباه کردم😔</t>
+  </si>
+  <si>
+    <t>چه معنی میده والا، هر چی دم دستم باشه شوت می‌کنم سمتش 🩴</t>
+  </si>
+  <si>
+    <t>عذرخواهی می‌کنم ولی ازش می‌خواهم از اینجا به بعد بیشتر حواسش به نظم خونه باشه✋🏼</t>
+  </si>
+  <si>
+    <t>عاشق بستنیه، برای اینکه از دلش دربیارم سریع میپرم براش بستنی می‌خرم 🍦</t>
+  </si>
+  <si>
+    <t>حالا یه اشتباهی کردم دیگه برای همین به روی خودم نمیارم و بحث و ناراحتی رو ادامه نمی‌دم🙂</t>
+  </si>
+  <si>
+    <t>مهمون اومده و بچتون نمی‌خواد توی مهمونی شرکت کنه و میخواد تو  اتاقش بمونه. از شما هم می‌خواد از مهمون‌ها پنهان کنین که تو اتاقه 🫢</t>
+  </si>
+  <si>
+    <t>دلیل بی‌میلیش برای نبودن در مهمونی رو می‌پرسم</t>
+  </si>
+  <si>
+    <t>به زور در اتاقشو باز می‌ذارم و بلند به همه مهمونا می‌گم که خونه‌اس تا بلکم خجالت بکشه</t>
+  </si>
+  <si>
+    <t>خط قرمز پنهان‌کاری و دروغگویی رو دوباره بهش گوشزد می‌کنم</t>
+  </si>
+  <si>
+    <t>خب ناراحت می‌شم که نمی‌خواد تو مهمونی شرکت کنه و بهش هم میگم ولی خب به حرفش عمل می‌کنم</t>
+  </si>
+  <si>
+    <t>وقت انتخاب رشته دبیرستان فرزندتون رسیده. و شما فکر می‌کنید انتخابش آینده شغلی و تحصیلی خوبی نداره و عاقلانه نیست 📚</t>
+  </si>
+  <si>
+    <t>دختر عمه پروین رو بهش یاداوری می‌کنم که چه تجربه ناموفقی داشته😥</t>
+  </si>
+  <si>
+    <t>تلاش می‌کنم تجربه کوتاهی در رشته‌های دیگر پیدا کنه🤓</t>
+  </si>
+  <si>
+    <t>چون  حال خوبش برام مهمتر از همه چیزه اجازه می‌دهم خودش انتخاب کنه😌</t>
+  </si>
+  <si>
+    <t>اگر خیلی اصرار به رشته خاصی کنه می‌گم دیگه نمی‌خواد درس بخونی🙂</t>
+  </si>
+  <si>
+    <t>یکبار مسیر کلی که با هم طراحی کردیم رو بررسی می‌کنیم تا متوجه شویم این رشته اصلا به پول می‌رسه یا نه😊</t>
+  </si>
+  <si>
+    <t>برای تفریح رفتین پارک، اجازه میدین از چه وسیله‌ای استفاده کنه 🎡</t>
+  </si>
+  <si>
+    <t>فقط یک وسیله اونم در زمان محدود⏰</t>
+  </si>
+  <si>
+    <t>استخر توپ⚽️</t>
+  </si>
+  <si>
+    <t>هر چی دلش بخواد 🎢</t>
+  </si>
+  <si>
+    <t>تاب سواری🎠</t>
+  </si>
+  <si>
+    <t>بازی در جای سربسته🏰</t>
+  </si>
+  <si>
+    <t>فرض کنید فرزند ۱۲ ساله‌ای دارید که می‌خواد آشپزی کنه:🍝</t>
+  </si>
+  <si>
+    <t>یه لیست از غذاهایی که فکر میکنم آماده کردنش برایش راحتتره بهش می‌دم🧀</t>
+  </si>
+  <si>
+    <t>تمام مدت کنارش می‌مونم که اگر کمکی خواست باشم و سعی میکنم فیلم هم بگیرم که خاطره بشه🎥</t>
+  </si>
+  <si>
+    <t>وا آشپزخونه جای کسی جز خودم نیست حتما اونجا رو به هم میریزه من باید ۵ ساعت وایستم تمیز کنم🧹</t>
+  </si>
+  <si>
+    <t>وسایل مورد نیازش رو براش فراهم می‌کنم🥚</t>
+  </si>
+  <si>
+    <t>اینجوری که نمیشه، ازش می‌خوام فقط تو آماده کردن بخشی از غذا به من کمک کنه🍴</t>
   </si>
 </sst>
 </file>
@@ -515,13 +518,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -532,13 +535,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -549,13 +552,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -566,13 +569,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -589,7 +592,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -600,13 +603,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -617,13 +620,13 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -634,13 +637,13 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -651,13 +654,13 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -668,13 +671,13 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E11">
         <v>4</v>
@@ -685,13 +688,13 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -702,13 +705,13 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -719,13 +722,13 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E14">
         <v>4</v>
@@ -736,13 +739,13 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -753,13 +756,13 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -770,13 +773,13 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -787,30 +790,30 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -821,13 +824,13 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -838,13 +841,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
       </c>
       <c r="D21" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -855,13 +858,13 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -872,13 +875,13 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E23">
         <v>4</v>
@@ -889,13 +892,13 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -906,13 +909,13 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -923,13 +926,13 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -937,5 +940,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>